--- a/StructureDefinition-SEEHDSMedicationStatement.xlsx
+++ b/StructureDefinition-SEEHDSMedicationStatement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSMedicationStatement.xlsx
+++ b/StructureDefinition-SEEHDSMedicationStatement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSMedicationStatement.xlsx
+++ b/StructureDefinition-SEEHDSMedicationStatement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSMedicationStatement.xlsx
+++ b/StructureDefinition-SEEHDSMedicationStatement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSMedicationStatement.xlsx
+++ b/StructureDefinition-SEEHDSMedicationStatement.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSMedicationStatement.xlsx
+++ b/StructureDefinition-SEEHDSMedicationStatement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSMedicationStatement.xlsx
+++ b/StructureDefinition-SEEHDSMedicationStatement.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -941,7 +941,7 @@
 Reference(http://hl7.eu/fhir/base/StructureDefinition/medication-eu-core)</t>
   </si>
   <si>
-    <t>Läkemedel (medicationMedicalRecordBody.medicationPrescription.drug – XOR: unstructured/merchandise/drugArticle/drug/generics, se MED-003)</t>
+    <t>Läkemedel (medicationMedicalRecordBody.medicationPrescription.drug – exakt ett av unstructured/merchandise/drugArticle/drug/generics, se invarianten getmedicationhistory-drug-choice)</t>
   </si>
   <si>
     <t>Identifies the medication being administered. This is either a link to a resource representing the details of the medication or a simple attribute carrying a code that identifies the medication from a known list of medications.</t>

--- a/StructureDefinition-SEEHDSMedicationStatement.xlsx
+++ b/StructureDefinition-SEEHDSMedicationStatement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSMedicationStatement.xlsx
+++ b/StructureDefinition-SEEHDSMedicationStatement.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$77</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2763" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2800" uniqueCount="534">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1119,6 +1119,12 @@
     <t>DR.2</t>
   </si>
   <si>
+    <t>MedicationStatement.effective[x]:effectiveDateTime</t>
+  </si>
+  <si>
+    <t>effectiveDateTime</t>
+  </si>
+  <si>
     <t>MedicationStatement.dateAsserted</t>
   </si>
   <si>
@@ -1656,6 +1662,10 @@
   </si>
   <si>
     <t>Dosage.maxDosePerAdministration</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>not supported</t>
@@ -1990,12 +2000,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN76"/>
+  <dimension ref="A1:AN77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.10546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="45.9375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.70703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="15.40234375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -7482,14 +7492,16 @@
         <v>350</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7501,7 +7513,7 @@
         <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>77</v>
@@ -7513,12 +7525,14 @@
         <v>334</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>352</v>
+        <v>317</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7567,7 +7581,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>351</v>
+        <v>315</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7582,13 +7596,13 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>77</v>
+        <v>321</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>355</v>
+        <v>323</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7596,10 +7610,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7619,16 +7633,16 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7679,7 +7693,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7697,21 +7711,21 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7722,10 +7736,10 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>77</v>
@@ -7734,17 +7748,15 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7793,13 +7805,13 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
@@ -7811,21 +7823,21 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7839,7 +7851,7 @@
         <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>77</v>
@@ -7848,16 +7860,16 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7883,13 +7895,13 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>373</v>
+        <v>77</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -7907,7 +7919,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7922,24 +7934,24 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>374</v>
+        <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>376</v>
+        <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7953,7 +7965,7 @@
         <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>77</v>
@@ -7962,16 +7974,16 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>378</v>
+        <v>218</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7997,13 +8009,13 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>77</v>
+        <v>375</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -8021,7 +8033,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8036,24 +8048,24 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8067,7 +8079,7 @@
         <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>77</v>
@@ -8076,15 +8088,17 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8133,7 +8147,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8148,13 +8162,13 @@
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>77</v>
+        <v>378</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8162,10 +8176,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8188,17 +8202,15 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>394</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8247,7 +8259,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8262,10 +8274,10 @@
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>77</v>
+        <v>390</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8274,12 +8286,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8290,10 +8302,10 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>77</v>
@@ -8302,15 +8314,17 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>102</v>
+        <v>393</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>103</v>
+        <v>394</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8359,25 +8373,25 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>105</v>
+        <v>392</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>106</v>
+        <v>397</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8388,21 +8402,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -8414,17 +8428,15 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8461,31 +8473,31 @@
         <v>77</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
@@ -8502,14 +8514,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>399</v>
+        <v>108</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8522,26 +8534,24 @@
         <v>77</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>109</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>400</v>
+        <v>110</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>401</v>
+        <v>111</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="O58" t="s" s="2">
-        <v>243</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8577,19 +8587,19 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>402</v>
+        <v>116</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8607,7 +8617,7 @@
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8618,43 +8628,45 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>77</v>
+        <v>401</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>404</v>
+        <v>109</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="O59" t="s" s="2">
-        <v>407</v>
+        <v>243</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8703,39 +8715,39 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>409</v>
+        <v>187</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>410</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8749,7 +8761,7 @@
         <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>77</v>
@@ -8758,17 +8770,17 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>102</v>
+        <v>406</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8817,7 +8829,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8835,21 +8847,21 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8860,10 +8872,10 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>77</v>
@@ -8872,19 +8884,17 @@
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>218</v>
+        <v>102</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8909,13 +8919,13 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>422</v>
+        <v>77</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>423</v>
+        <v>77</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -8933,13 +8943,13 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
@@ -8951,21 +8961,21 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>425</v>
+        <v>418</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8976,7 +8986,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>77</v>
@@ -8988,16 +8998,20 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>102</v>
+        <v>218</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
       </c>
@@ -9021,13 +9035,13 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>77</v>
+        <v>424</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>77</v>
+        <v>425</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -9045,13 +9059,13 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>77</v>
@@ -9063,21 +9077,21 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9091,7 +9105,7 @@
         <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>77</v>
@@ -9100,20 +9114,16 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>431</v>
+        <v>102</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
       </c>
@@ -9161,7 +9171,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9179,21 +9189,21 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>322</v>
+        <v>411</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>77</v>
+        <v>427</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9207,7 +9217,7 @@
         <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>77</v>
@@ -9216,18 +9226,20 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
@@ -9251,13 +9263,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>442</v>
+        <v>77</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>443</v>
+        <v>77</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9275,7 +9287,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9293,21 +9305,21 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>445</v>
+        <v>322</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>446</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9330,20 +9342,18 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>218</v>
+        <v>440</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9370,10 +9380,10 @@
         <v>154</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>77</v>
@@ -9391,7 +9401,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9409,21 +9419,21 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>456</v>
+        <v>448</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9437,7 +9447,7 @@
         <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>77</v>
@@ -9449,14 +9459,16 @@
         <v>218</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>451</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -9484,10 +9496,10 @@
         <v>154</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -9505,7 +9517,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9523,21 +9535,21 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9551,7 +9563,7 @@
         <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>77</v>
@@ -9563,16 +9575,14 @@
         <v>218</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>469</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -9600,10 +9610,10 @@
         <v>154</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
@@ -9621,7 +9631,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9639,21 +9649,21 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>475</v>
+        <v>467</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9664,7 +9674,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
@@ -9676,16 +9686,20 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>477</v>
+        <v>218</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>470</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
       </c>
@@ -9709,13 +9723,13 @@
         <v>77</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>77</v>
+        <v>473</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>77</v>
+        <v>474</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>77</v>
@@ -9733,13 +9747,13 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>77</v>
@@ -9751,21 +9765,21 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>77</v>
+        <v>476</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9776,7 +9790,7 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>77</v>
@@ -9785,16 +9799,16 @@
         <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>102</v>
+        <v>479</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>103</v>
+        <v>480</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>104</v>
+        <v>481</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9845,50 +9859,50 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>105</v>
+        <v>482</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>77</v>
+        <v>483</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
@@ -9900,17 +9914,15 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9947,31 +9959,31 @@
         <v>77</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
@@ -9988,21 +10000,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
@@ -10011,21 +10023,21 @@
         <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>218</v>
+        <v>109</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>485</v>
+        <v>110</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
       </c>
@@ -10049,63 +10061,63 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>488</v>
+        <v>77</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>489</v>
+        <v>77</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>490</v>
+        <v>116</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>491</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10128,19 +10140,17 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>493</v>
+        <v>218</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>496</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10165,13 +10175,13 @@
         <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>77</v>
+        <v>490</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>77</v>
+        <v>491</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -10189,7 +10199,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10207,21 +10217,21 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>474</v>
+        <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>499</v>
+        <v>493</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10244,19 +10254,19 @@
         <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10305,7 +10315,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10323,21 +10333,21 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>507</v>
+        <v>476</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>508</v>
+        <v>501</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10360,19 +10370,19 @@
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -10421,7 +10431,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10439,21 +10449,21 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>517</v>
+        <v>510</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10476,19 +10486,19 @@
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -10537,7 +10547,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10555,21 +10565,21 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>77</v>
+        <v>519</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10592,17 +10602,19 @@
         <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>523</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>524</v>
+      </c>
       <c r="O76" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10651,35 +10663,149 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="AG76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN76" t="s" s="2">
+      <c r="M77" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN76">
+  <autoFilter ref="A1:AN77">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10689,7 +10815,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI75">
+  <conditionalFormatting sqref="A2:AI76">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
